--- a/data/credit_bond_all_2026-10-14.xlsx
+++ b/data/credit_bond_all_2026-10-14.xlsx
@@ -7444,7 +7444,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26川宁生物SCP002</t>
+          <t>26东北电力SCP005</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>012682444.IB</t>
+          <t>012682443.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -7463,55 +7463,55 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.90</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>36.2</v>
+        <v>34.2</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26百业源CP003</t>
+          <t>26东北电力SCP004</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>267D</t>
+          <t>233D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.5169</t>
+          <t>1.5119</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>伊犁川宁生物技术股份有限公司</t>
+          <t>国家电投集团东北电力有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C+ 30.83</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-14 10:00</t>
+          <t>10-14 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -7535,40 +7535,38 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.81%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额2亿元，全部用于发行人本部补充营运资金</t>
+          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7579,7 +7577,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7589,7 +7587,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>伊犁川宁生物技术股份有限公司2026年度第二期超短期融资券</t>
+          <t>国家电投集团东北电力有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7625,27 +7623,27 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>生物制品</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7678,7 +7676,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26东北电力SCP005</t>
+          <t>26农投资本MTN001(乡村振兴)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7688,64 +7686,56 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>012682443.IB</t>
+          <t>102683982.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>34.2</v>
+        <v>53.06</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>26东北电力SCP004</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>233D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5119</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司</t>
+          <t>河南农投资本有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.83</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7760,7 +7750,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -7771,47 +7761,49 @@
       <c r="U33" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="V33" s="3"/>
+      <c r="V33" s="4" t="n">
+        <v>1.33</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务</t>
+          <t>本期债务融资工具发行拟募集资金【3】亿元,所募集资金拟用于偿还发行人下属子公司有息负债</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7821,7 +7813,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司2026年度第五期超短期融资券</t>
+          <t>河南农投资本有限公司2026年度第一期中期票据(乡村振兴)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7831,7 +7823,7 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2027-07-13</t>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7842,7 +7834,7 @@
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
@@ -7855,29 +7847,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+      <c r="AP33" s="3"/>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7905,12 +7893,14 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26农投资本MTN001(乡村振兴)</t>
+          <t>26三友化工MTN002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7920,7 +7910,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683982.IB</t>
+          <t>102684009.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7929,32 +7919,40 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>53.06</v>
+        <v>41.06</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>26三友化工MTN001</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>2.56Y</t>
+        </is>
+      </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7181</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7964,12 +7962,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>河南农投资本有限公司</t>
+          <t>唐山三友化工股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 10.74</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7984,7 +7982,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7993,19 +7991,17 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>1.33</v>
-      </c>
+        <v>3.92</v>
+      </c>
+      <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8016,17 +8012,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金【3】亿元,所募集资金拟用于偿还发行人下属子公司有息负债</t>
+          <t>本期发行金额为人民币5.00亿元,募集资金5亿元拟用于偿还存量债务</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中信银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -8047,7 +8043,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>河南农投资本有限公司2026年度第一期中期票据(乡村振兴)</t>
+          <t>唐山三友化工股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8068,7 +8064,7 @@
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
@@ -8081,25 +8077,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP34" s="3"/>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合化工</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合化工</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化学原料</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8127,14 +8127,12 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AZ34" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ34" s="3"/>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26三友化工MTN002</t>
+          <t>26北部湾MTN008A</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8144,7 +8142,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102684009.IB</t>
+          <t>102683980.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -8153,55 +8151,55 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.35 ~ 2.15</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>41.06</v>
+        <v>32.06</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26三友化工MTN001</t>
+          <t>26北部湾MTN007A</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.56Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.7181</t>
+          <t>1.7039</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6675</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>唐山三友化工股份有限公司</t>
+          <t>广西北部湾国际港务集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 10.74</t>
+          <t>C 25.70</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8211,12 +8209,12 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-14 09:00</t>
+          <t>10-14 11:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -8225,38 +8223,40 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="V35" s="3"/>
+        <v>7.5</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为人民币5.00亿元,募集资金5亿元拟用于偿还存量债务</t>
+          <t>本期债务融资工具基础发行金额为人民币0亿元，发行上限金额为人民币10亿元，其中8.905亿元用于偿还发行人有息债务，剩余1.095亿元用于补充发行人下属子公司流动资金。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>唐山三友化工股份有限公司2026年度第二期中期票据</t>
+          <t>广西北部湾国际港务集团有限公司2026年度第八期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8313,27 +8313,27 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>综合化工</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>综合化工</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>化学原料</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8366,17 +8366,17 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26北部湾MTN008A</t>
+          <t>26东国02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>10-15 18:00</t>
+          <t>10-14 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683980.IB</t>
+          <t>284221.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -8385,55 +8385,55 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 2.15</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>32.06</v>
+        <v>40.8</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26北部湾MTN007A</t>
+          <t>25东国01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>3.37Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7039</t>
+          <t>1.7323</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/1.6675</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾国际港务集团有限公司</t>
+          <t>北京市东城区国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C 25.70</t>
+          <t>C- 15.89</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-14 11:00</t>
+          <t>10-14 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8457,19 +8457,17 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>4.32</v>
+      </c>
+      <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8480,23 +8478,23 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>北京市-东城区</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为人民币0亿元，发行上限金额为人民币10亿元，其中8.905亿元用于偿还发行人有息债务，剩余1.095亿元用于补充发行人下属子公司流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后，全部用于偿还公司有息负债。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中邮证券有限责任公司,国新证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8506,17 +8504,17 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾国际港务集团有限公司2026年度第八期中期票据(品种一)</t>
+          <t>北京市东城区国有资本运营有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
@@ -8527,12 +8525,12 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
@@ -8542,7 +8540,7 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
@@ -8557,17 +8555,17 @@
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8592,7 +8590,7 @@
       </c>
       <c r="AY36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AZ36" s="3"/>
@@ -8600,7 +8598,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26东国02</t>
+          <t>26杭千02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8610,49 +8608,47 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>284221.SH</t>
+          <t>284246.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>40.8</v>
+        <v>47.04</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25东国01</t>
+          <t>建管VY02</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>3.37Y</t>
+          <t>2.16Y+N</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.7323</t>
+          <t>1.7760</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8662,12 +8658,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>北京市东城区国有资本运营有限公司</t>
+          <t>杭州杭千高速公路发展有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 15.89</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8691,19 +8687,15 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>4.32</v>
+        <v>1.71</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t>1.67%~1.77%</t>
-        </is>
-      </c>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X37" s="3"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8712,17 +8704,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>北京市-东城区</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后，全部用于偿还公司有息负债。</t>
+          <t>本期债券募集资金不超过8亿元(含8亿元),扣除发行费用后拟用于偿还公司有息债务</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中邮证券有限责任公司,国新证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8743,7 +8735,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>北京市东城区国有资本运营有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>杭州杭千高速公路发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8753,7 +8745,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-10-16</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8764,7 +8756,7 @@
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
@@ -8774,14 +8766,10 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP37" s="3"/>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
           <t>基础设施投融资</t>
@@ -8789,17 +8777,17 @@
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8832,57 +8820,59 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26杭千02</t>
+          <t>26铁道17</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>10-14 19:00</t>
+          <t>10-14 11:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>284246.SH</t>
+          <t>2680035.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>50.0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>50.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.08 ~ 2.08</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>47.04</v>
+        <v>6.84</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>建管VY02</t>
+          <t>16铁道06</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.16Y+N</t>
+          <t>10.01Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.7760</t>
+          <t>1.7832</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8892,12 +8882,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>杭州杭千高速公路发展有限公司</t>
+          <t>中国国家铁路集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 18.00</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8907,7 +8897,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-14 15:00</t>
+          <t>10-14 10:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8917,16 +8907,18 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V38" s="3"/>
+        <v>2.738</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>1.0204</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X38" s="3"/>
@@ -8935,103 +8927,115 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z38" s="3"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过8亿元(含8亿元),扣除发行费用后拟用于偿还公司有息债务</t>
+          <t>本期债券发行募集资金100亿元，其中98.4187亿元用于铁路项目建设，1.5813亿元用于债务结构调整。上述资金的使用，将有利于增强发行人可持续发展能力。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3"/>
+          <t>中信证券股份有限公司,国开证券股份有限公司,华泰联合证券有限责任公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>铁路建设基金</t>
+        </is>
+      </c>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>政府支持债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>杭州杭千高速公路发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>2026年第十三期中国铁路建设债券(10年期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2036-10-15</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP38" s="3"/>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -20938,17 +20942,17 @@
     <row r="90" customHeight="true" ht="18.0">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>26民生银行债02</t>
+          <t>26鲁高K2</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>10-14 17:00</t>
+          <t>10-14 19:00</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>212680065.IB</t>
+          <t>246220.SH</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -20957,55 +20961,55 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>26民生银行债01</t>
+          <t>24鲁高K4</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>3.04Y</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>--/1.5650</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>A+ 81.83</t>
+          <t>B- 43.51</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -21015,7 +21019,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>10-14 09:00</t>
+          <t>10-14 15:00</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -21028,7 +21032,9 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="U90" s="3"/>
+      <c r="U90" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="V90" s="3"/>
       <c r="W90" s="3" t="inlineStr">
         <is>
@@ -21037,7 +21043,7 @@
       </c>
       <c r="X90" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.52%~1.62%</t>
         </is>
       </c>
       <c r="Y90" s="3" t="inlineStr">
@@ -21048,38 +21054,38 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB90" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债券拟募集资金10亿元,扣除发行费用后拟将不超过7亿元用于物流网项目建设,不超过3亿元用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC90" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
+          <t>广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF90" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG90" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH90" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司2026年金融债券(第二期)</t>
+          <t>山东高速集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(物流网建设)</t>
         </is>
       </c>
       <c r="AI90" s="3" t="inlineStr">
@@ -21095,12 +21101,12 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AM90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AN90" s="3" t="inlineStr">
@@ -21110,32 +21116,32 @@
       </c>
       <c r="AO90" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP90" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ90" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR90" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS90" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT90" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU90" s="3" t="inlineStr">
@@ -21168,7 +21174,7 @@
     <row r="91" customHeight="true" ht="18.0">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>26鲁高K2</t>
+          <t>26光证G8</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -21178,64 +21184,64 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>246220.SH</t>
+          <t>246091.SH</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>31.8</v>
+        <v>30.04</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>24鲁高K4</t>
+          <t>26光证G6</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>3.04Y</t>
+          <t>4.84Y</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.6797</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>1.6950/1.6600</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>B- 43.51</t>
+          <t>B- 44.43</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -21259,17 +21265,17 @@
         </is>
       </c>
       <c r="U91" s="4" t="n">
-        <v>3.9</v>
+        <v>2.524</v>
       </c>
       <c r="V91" s="3"/>
       <c r="W91" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X91" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.62%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y91" s="3" t="inlineStr">
@@ -21277,31 +21283,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z91" s="3"/>
+      <c r="Z91" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA91" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB91" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金10亿元,扣除发行费用后拟将不超过7亿元用于物流网项目建设,不超过3亿元用于偿还有息债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟全部用于偿还到期公司债券本金、补充流动资金[21光证G5,23光证G3]</t>
         </is>
       </c>
       <c r="AC91" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
+          <t>兴业证券股份有限公司,招商证券股份有限公司,东方证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD91" s="3"/>
       <c r="AE91" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF91" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG91" s="3" t="inlineStr">
@@ -21311,7 +21321,7 @@
       </c>
       <c r="AH91" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(物流网建设)</t>
+          <t>光大证券股份有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI91" s="3" t="inlineStr">
@@ -21321,7 +21331,7 @@
       </c>
       <c r="AJ91" s="3" t="inlineStr">
         <is>
-          <t>2029-10-16</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK91" s="3"/>
@@ -21342,32 +21352,32 @@
       </c>
       <c r="AO91" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP91" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ91" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR91" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS91" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT91" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU91" s="3" t="inlineStr">
@@ -21400,7 +21410,7 @@
     <row r="92" customHeight="true" ht="18.0">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>26光证G8</t>
+          <t>26动能03</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -21410,64 +21420,64 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>246091.SH</t>
+          <t>246176.SH</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>30.04</v>
+        <v>13.04</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>26光证G6</t>
+          <t>26动能02</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>4.84Y</t>
+          <t>2.50Y+2.00Y</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>1.6797</t>
+          <t>1.6623</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>1.6950/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
+          <t>山东省新动能基金管理有限公司</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>B- 44.43</t>
+          <t>C- 24.50</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21477,7 +21487,7 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>10-14 15:00</t>
+          <t>10-14 16:00</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr">
@@ -21491,17 +21501,17 @@
         </is>
       </c>
       <c r="U92" s="4" t="n">
-        <v>2.524</v>
+        <v>3.77</v>
       </c>
       <c r="V92" s="3"/>
       <c r="W92" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X92" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y92" s="3" t="inlineStr">
@@ -21509,35 +21519,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z92" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z92" s="3"/>
       <c r="AA92" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB92" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟全部用于偿还到期公司债券本金、补充流动资金[21光证G5,23光证G3]</t>
+          <t>本次公司债券募集资金扣除发行费用后拟全部用于偿还回售公司债券本金[23动能03]</t>
         </is>
       </c>
       <c r="AC92" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,招商证券股份有限公司,东方证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD92" s="3"/>
       <c r="AE92" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF92" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG92" s="3" t="inlineStr">
@@ -21547,7 +21553,7 @@
       </c>
       <c r="AH92" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
+          <t>山东省新动能基金管理有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI92" s="3" t="inlineStr">
@@ -21581,11 +21587,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP92" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+      <c r="AP92" s="3"/>
       <c r="AQ92" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -21593,22 +21595,22 @@
       </c>
       <c r="AR92" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS92" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT92" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU92" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AV92" s="3" t="inlineStr">
@@ -21618,7 +21620,7 @@
       </c>
       <c r="AW92" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX92" s="3" t="inlineStr">
@@ -21636,7 +21638,7 @@
     <row r="93" customHeight="true" ht="18.0">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>26动能03</t>
+          <t>26投控01</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -21646,30 +21648,30 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>246176.SH</t>
+          <t>246157.SH</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H93" s="4" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13.04</v>
+        <v>22.04</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -21678,17 +21680,17 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>26动能02</t>
+          <t>25投控03</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>2.50Y+2.00Y</t>
+          <t>3.79Y</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>1.6623</t>
+          <t>1.6498</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -21698,12 +21700,12 @@
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>山东省新动能基金管理有限公司</t>
+          <t>苏州工业园区国有资本投资运营控股有限公司</t>
         </is>
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>C- 24.50</t>
+          <t>C 26.19</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21727,17 +21729,17 @@
         </is>
       </c>
       <c r="U93" s="4" t="n">
-        <v>3.77</v>
+        <v>5.37</v>
       </c>
       <c r="V93" s="3"/>
       <c r="W93" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X93" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y93" s="3" t="inlineStr">
@@ -21748,17 +21750,17 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB93" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后拟全部用于偿还回售公司债券本金[23动能03]</t>
+          <t>本期公司债券募集资金10.00亿元扣除发行费用后,拟用于偿还到期有息债务[G21苏国资01]</t>
         </is>
       </c>
       <c r="AC93" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,江海证券有限公司</t>
         </is>
       </c>
       <c r="AD93" s="3"/>
@@ -21779,7 +21781,7 @@
       </c>
       <c r="AH93" s="3" t="inlineStr">
         <is>
-          <t>山东省新动能基金管理有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>苏州工业园区国有资本投资运营控股有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI93" s="3" t="inlineStr">
@@ -21800,7 +21802,7 @@
       </c>
       <c r="AM93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AN93" s="3" t="inlineStr">
@@ -21810,33 +21812,37 @@
       </c>
       <c r="AO93" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP93" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP93" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ93" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR93" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS93" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT93" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU93" s="3" t="inlineStr">
         <is>
-          <t>2029-10-16</t>
+          <t/>
         </is>
       </c>
       <c r="AV93" s="3" t="inlineStr">
@@ -21846,7 +21852,7 @@
       </c>
       <c r="AW93" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX93" s="3" t="inlineStr">
@@ -21864,7 +21870,7 @@
     <row r="94" customHeight="true" ht="18.0">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>26投控01</t>
+          <t>26乌江Y1</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -21874,98 +21880,98 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>246157.SH</t>
+          <t>246206.SH</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>22.04</v>
+        <v>45.8</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>24乌江能源MTN001</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>2.81Y</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>1.6783</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>贵州乌江能源投资有限公司</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.12</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="inlineStr">
+        <is>
+          <t>10-14 15:00</t>
+        </is>
+      </c>
+      <c r="S94" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>25投控03</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>3.79Y</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>1.6498</t>
-        </is>
-      </c>
-      <c r="N94" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O94" s="3" t="inlineStr">
-        <is>
-          <t>苏州工业园区国有资本投资运营控股有限公司</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="inlineStr">
-        <is>
-          <t>C 26.19</t>
-        </is>
-      </c>
-      <c r="Q94" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="R94" s="3" t="inlineStr">
-        <is>
-          <t>10-14 16:00</t>
-        </is>
-      </c>
-      <c r="S94" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T94" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
       <c r="U94" s="4" t="n">
-        <v>5.37</v>
+        <v>3.46</v>
       </c>
       <c r="V94" s="3"/>
       <c r="W94" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X94" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y94" s="3" t="inlineStr">
@@ -21976,17 +21982,17 @@
       <c r="Z94" s="3"/>
       <c r="AA94" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="AB94" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金10.00亿元扣除发行费用后,拟用于偿还到期有息债务[G21苏国资01]</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟将10亿元用于股权投资,5亿元用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC94" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,江海证券有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD94" s="3"/>
@@ -22007,7 +22013,7 @@
       </c>
       <c r="AH94" s="3" t="inlineStr">
         <is>
-          <t>苏州工业园区国有资本投资运营控股有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>贵州乌江能源投资有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI94" s="3" t="inlineStr">
@@ -22017,7 +22023,7 @@
       </c>
       <c r="AJ94" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AK94" s="3"/>
@@ -22028,7 +22034,7 @@
       </c>
       <c r="AM94" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AN94" s="3" t="inlineStr">
@@ -22038,32 +22044,32 @@
       </c>
       <c r="AO94" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP94" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ94" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR94" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS94" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT94" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU94" s="3" t="inlineStr">
@@ -22078,7 +22084,7 @@
       </c>
       <c r="AW94" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX94" s="3" t="inlineStr">
@@ -22096,7 +22102,7 @@
     <row r="95" customHeight="true" ht="18.0">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>26乌江Y1</t>
+          <t>26翔业02</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -22106,49 +22112,49 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>246206.SH</t>
+          <t>246171.SH</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H95" s="4" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>45.8</v>
+        <v>27.8</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>24乌江能源MTN001</t>
+          <t>26翔业01</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>2.73Y</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>1.6783</t>
+          <t>1.6023</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -22158,12 +22164,12 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江能源投资有限公司</t>
+          <t>厦门翔业集团有限公司</t>
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>C- 18.12</t>
+          <t>C 27.75</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -22187,17 +22193,17 @@
         </is>
       </c>
       <c r="U95" s="4" t="n">
-        <v>3.46</v>
+        <v>4.09</v>
       </c>
       <c r="V95" s="3"/>
       <c r="W95" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X95" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.54%~1.64%</t>
         </is>
       </c>
       <c r="Y95" s="3" t="inlineStr">
@@ -22208,17 +22214,17 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB95" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟将10亿元用于股权投资,5亿元用于偿还到期债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金[24翔业04]</t>
         </is>
       </c>
       <c r="AC95" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD95" s="3"/>
@@ -22239,7 +22245,7 @@
       </c>
       <c r="AH95" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江能源投资有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>厦门翔业集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI95" s="3" t="inlineStr">
@@ -22260,7 +22266,7 @@
       </c>
       <c r="AM95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AN95" s="3" t="inlineStr">
@@ -22275,27 +22281,27 @@
       </c>
       <c r="AP95" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ95" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR95" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS95" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT95" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>机场</t>
         </is>
       </c>
       <c r="AU95" s="3" t="inlineStr">
@@ -22310,7 +22316,7 @@
       </c>
       <c r="AW95" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX95" s="3" t="inlineStr">
@@ -22328,74 +22334,74 @@
     <row r="96" customHeight="true" ht="18.0">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>26翔业02</t>
+          <t>26郑州交发MTN003(绿色)</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>10-14 19:00</t>
+          <t>10-15 18:00</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>246171.SH</t>
+          <t>102684010.IB</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>27.8</v>
+        <v>41.06</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>26翔业01</t>
+          <t>26郑州交发MTN002(绿色)</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2.73Y</t>
+          <t>2.95Y+N</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>1.6023</t>
+          <t>1.6865</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>厦门翔业集团有限公司</t>
+          <t>郑州交通发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>C 27.75</t>
+          <t>B- 38.14</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -22405,7 +22411,7 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>10-14 15:00</t>
+          <t>10-14 09:00</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr">
@@ -22419,17 +22425,19 @@
         </is>
       </c>
       <c r="U96" s="4" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="V96" s="3"/>
+        <v>4.4</v>
+      </c>
+      <c r="V96" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W96" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X96" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.64%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y96" s="3" t="inlineStr">
@@ -22440,23 +22448,23 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB96" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金[24翔业04]</t>
+          <t>本期发行金额5.00亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
         </is>
       </c>
       <c r="AC96" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,兴业证券股份有限公司</t>
+          <t>中国工商银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD96" s="3"/>
       <c r="AE96" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF96" s="3" t="inlineStr">
@@ -22466,12 +22474,12 @@
       </c>
       <c r="AG96" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH96" s="3" t="inlineStr">
         <is>
-          <t>厦门翔业集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>郑州交通发展投资集团有限公司2026年度第三期绿色中期票据</t>
         </is>
       </c>
       <c r="AI96" s="3" t="inlineStr">
@@ -22487,54 +22495,54 @@
       <c r="AK96" s="3"/>
       <c r="AL96" s="3" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AM96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AN96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AO96" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP96" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ96" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR96" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS96" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT96" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU96" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM96" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AN96" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AO96" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP96" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ96" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR96" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AS96" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AT96" s="3" t="inlineStr">
-        <is>
-          <t>机场</t>
-        </is>
-      </c>
-      <c r="AU96" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV96" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -22542,17 +22550,17 @@
       </c>
       <c r="AW96" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX96" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AZ96" s="3"/>
@@ -22560,74 +22568,74 @@
     <row r="97" customHeight="true" ht="18.0">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>26郑州交发MTN003(绿色)</t>
+          <t>26金临01</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>10-15 18:00</t>
+          <t>10-14 19:00</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>102684010.IB</t>
+          <t>284174.SH</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H97" s="4" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>41.06</v>
+        <v>35.04</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>26郑州交发MTN002(绿色)</t>
+          <t>26高城01</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+N</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>1.6865</t>
+          <t>1.6972</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司</t>
+          <t>上海金桥临港综合区投资开发有限公司</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>B- 38.14</t>
+          <t>D- 2.50</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -22637,7 +22645,7 @@
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>10-14 09:00</t>
+          <t>10-14 15:00</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr">
@@ -22651,46 +22659,44 @@
         </is>
       </c>
       <c r="U97" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V97" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>2.08</v>
+      </c>
+      <c r="V97" s="3"/>
       <c r="W97" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X97" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y97" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z97" s="3"/>
       <c r="AA97" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>上海市-浦东新区</t>
         </is>
       </c>
       <c r="AB97" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额5.00亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
+          <t>本期债券募集资金不超过人民币11亿元(含11亿元),拟全部用于偿还回售公司债券本金[23金临01]</t>
         </is>
       </c>
       <c r="AC97" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,中国银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD97" s="3"/>
       <c r="AE97" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF97" s="3" t="inlineStr">
@@ -22700,28 +22706,28 @@
       </c>
       <c r="AG97" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH97" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司2026年度第三期绿色中期票据</t>
+          <t>上海金桥临港综合区投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI97" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ97" s="3" t="inlineStr">
         <is>
-          <t>2029-10-16</t>
+          <t>2031-10-16</t>
         </is>
       </c>
       <c r="AK97" s="3"/>
       <c r="AL97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AM97" s="3" t="inlineStr">
@@ -22736,12 +22742,12 @@
       </c>
       <c r="AO97" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP97" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ97" s="3" t="inlineStr">
@@ -22751,22 +22757,22 @@
       </c>
       <c r="AR97" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS97" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT97" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU97" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AV97" s="3" t="inlineStr">
@@ -22776,17 +22782,17 @@
       </c>
       <c r="AW97" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX97" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AZ97" s="3"/>
@@ -22794,29 +22800,29 @@
     <row r="98" customHeight="true" ht="18.0">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>26金临01</t>
+          <t>26拱墅经投PPN002</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>10-14 19:00</t>
+          <t>10-14 18:00</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>284174.SH</t>
+          <t>032680547.IB</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>11.0</v>
+        <v>7.5</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>11.0</v>
+        <v>7.5</v>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
@@ -22824,29 +22830,29 @@
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>35.04</v>
+        <v>40.04</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>26高城01</t>
+          <t>26拱墅经投PPN001</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>1.6972</t>
+          <t>1.8149</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -22856,12 +22862,12 @@
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>上海金桥临港综合区投资开发有限公司</t>
+          <t>杭州市拱墅区经济发展投资有限公司</t>
         </is>
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>D- 2.50</t>
+          <t>C- 19.67</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -22871,21 +22877,21 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>10-14 15:00</t>
+          <t>10-14 14:00</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="T98" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="U98" s="4" t="n">
-        <v>2.08</v>
+        <v>4.1733</v>
       </c>
       <c r="V98" s="3"/>
       <c r="W98" s="3" t="inlineStr">
@@ -22895,7 +22901,7 @@
       </c>
       <c r="X98" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y98" s="3" t="inlineStr">
@@ -22906,23 +22912,23 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3" t="inlineStr">
         <is>
-          <t>上海市-浦东新区</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB98" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过人民币11亿元(含11亿元),拟全部用于偿还回售公司债券本金[23金临01]</t>
+          <t>本期债券发行基础规模为0亿元,发行金额上限为7.5亿元,募集资金拟用于偿还发行人本级有息债务7.5亿元[23拱墅经投PPN002]</t>
         </is>
       </c>
       <c r="AC98" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>财通证券股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD98" s="3"/>
       <c r="AE98" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF98" s="3" t="inlineStr">
@@ -22932,12 +22938,12 @@
       </c>
       <c r="AG98" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH98" s="3" t="inlineStr">
         <is>
-          <t>上海金桥临港综合区投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>杭州市拱墅区经济发展投资有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI98" s="3" t="inlineStr">
@@ -22947,60 +22953,60 @@
       </c>
       <c r="AJ98" s="3" t="inlineStr">
         <is>
-          <t>2031-10-16</t>
+          <t>2031-10-15</t>
         </is>
       </c>
       <c r="AK98" s="3"/>
       <c r="AL98" s="3" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AM98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AN98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AO98" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP98" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ98" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR98" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS98" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT98" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU98" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM98" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AN98" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AO98" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP98" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
-      <c r="AQ98" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR98" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS98" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT98" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU98" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-16</t>
-        </is>
-      </c>
       <c r="AV98" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -23008,7 +23014,7 @@
       </c>
       <c r="AW98" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX98" s="3" t="inlineStr">
@@ -23026,74 +23032,74 @@
     <row r="99" customHeight="true" ht="18.0">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>26拱墅经投PPN002</t>
+          <t>26铁道18</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>10-14 18:00</t>
+          <t>10-14 11:00</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>032680547.IB</t>
+          <t>2680036.IB</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>7.5</v>
+        <v>50.0</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>7.5</v>
+        <v>50.0</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.48 ~ 2.48</t>
         </is>
       </c>
       <c r="H99" s="4" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>40.04</v>
+        <v>16.0</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>26拱墅经投PPN001</t>
+          <t>G26铁道6</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>29.92Y</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>1.8149</t>
+          <t>2.2147</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2100/2.2050</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>杭州市拱墅区经济发展投资有限公司</t>
+          <t>中国国家铁路集团有限公司</t>
         </is>
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>C- 19.67</t>
+          <t>C- 18.00</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -23103,12 +23109,12 @@
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>10-14 14:00</t>
+          <t>10-14 10:00</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T99" s="3" t="inlineStr">
@@ -23117,49 +23123,55 @@
         </is>
       </c>
       <c r="U99" s="4" t="n">
-        <v>4.1733</v>
-      </c>
-      <c r="V99" s="3"/>
+        <v>4.41</v>
+      </c>
+      <c r="V99" s="4" t="n">
+        <v>10.6739</v>
+      </c>
       <c r="W99" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X99" s="3" t="inlineStr">
-        <is>
-          <t>1.79%~1.89%</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X99" s="3"/>
       <c r="Y99" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z99" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z99" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA99" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="AB99" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行基础规模为0亿元,发行金额上限为7.5亿元,募集资金拟用于偿还发行人本级有息债务7.5亿元[23拱墅经投PPN002]</t>
+          <t>本期债券发行募集资金100亿元，其中98.4187亿元用于铁路项目建设，1.5813亿元用于债务结构调整。上述资金的使用，将有利于增强发行人可持续发展能力。</t>
         </is>
       </c>
       <c r="AC99" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,杭州银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD99" s="3"/>
+          <t>中信证券股份有限公司,国开证券股份有限公司,华泰联合证券有限责任公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD99" s="3" t="inlineStr">
+        <is>
+          <t>铁路建设基金</t>
+        </is>
+      </c>
       <c r="AE99" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>政府支持债券</t>
         </is>
       </c>
       <c r="AF99" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG99" s="3" t="inlineStr">
@@ -23169,28 +23181,32 @@
       </c>
       <c r="AH99" s="3" t="inlineStr">
         <is>
-          <t>杭州市拱墅区经济发展投资有限公司2026年度第二期定向债务融资工具</t>
+          <t>2026年第十三期中国铁路建设债券(30年期)</t>
         </is>
       </c>
       <c r="AI99" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ99" s="3" t="inlineStr">
         <is>
-          <t>2031-10-15</t>
-        </is>
-      </c>
-      <c r="AK99" s="3"/>
+          <t>2056-10-15</t>
+        </is>
+      </c>
+      <c r="AK99" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AM99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AN99" s="3" t="inlineStr">
@@ -23200,32 +23216,32 @@
       </c>
       <c r="AO99" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP99" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ99" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR99" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AS99" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>非盈利性交运服务</t>
         </is>
       </c>
       <c r="AT99" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU99" s="3" t="inlineStr">
@@ -23235,7 +23251,7 @@
       </c>
       <c r="AV99" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW99" s="3" t="inlineStr">
@@ -23258,59 +23274,59 @@
     <row r="100" customHeight="true" ht="18.0">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>26铁道17</t>
+          <t>26民生银行债02</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>10-14 11:00</t>
+          <t>10-14 17:00</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>2680035.IB</t>
+          <t>212680065.IB</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>1.08 ~ 2.08</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>6.84</v>
+        <v>30.8</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>16铁道06</t>
+          <t>26民生银行债01</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>10.01Y</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>1.7832</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -23320,12 +23336,12 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>中国国家铁路集团有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>C- 18.00</t>
+          <t>A+ 81.83</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -23335,7 +23351,7 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>10-14 10:00</t>
+          <t>10-14 09:00</t>
         </is>
       </c>
       <c r="S100" s="3" t="inlineStr">
@@ -23345,59 +23361,51 @@
       </c>
       <c r="T100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="U100" s="4" t="n">
-        <v>2.738</v>
-      </c>
-      <c r="V100" s="4" t="n">
-        <v>1.0204</v>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
       <c r="W100" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X100" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X100" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y100" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z100" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z100" s="3"/>
       <c r="AA100" s="3" t="inlineStr">
         <is>
-          <t>中华人民共和国</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB100" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行募集资金100亿元，其中98.4187亿元用于铁路项目建设，1.5813亿元用于债务结构调整。上述资金的使用，将有利于增强发行人可持续发展能力。</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC100" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国开证券股份有限公司,华泰联合证券有限责任公司,国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD100" s="3" t="inlineStr">
-        <is>
-          <t>铁路建设基金</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD100" s="3"/>
       <c r="AE100" s="3" t="inlineStr">
         <is>
-          <t>政府支持债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF100" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG100" s="3" t="inlineStr">
@@ -23407,7 +23415,7 @@
       </c>
       <c r="AH100" s="3" t="inlineStr">
         <is>
-          <t>2026年第十三期中国铁路建设债券(10年期)</t>
+          <t>中国民生银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI100" s="3" t="inlineStr">
@@ -23417,7 +23425,7 @@
       </c>
       <c r="AJ100" s="3" t="inlineStr">
         <is>
-          <t>2036-10-15</t>
+          <t>2029-10-16</t>
         </is>
       </c>
       <c r="AK100" s="3"/>
@@ -23433,37 +23441,37 @@
       </c>
       <c r="AN100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AO100" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP100" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ100" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR100" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS100" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT100" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU100" s="3" t="inlineStr">
@@ -23473,7 +23481,7 @@
       </c>
       <c r="AV100" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW100" s="3" t="inlineStr">
@@ -23496,74 +23504,74 @@
     <row r="101" customHeight="true" ht="18.0">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>26铁道18</t>
+          <t>26川宁生物SCP002</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>10-14 11:00</t>
+          <t>10-15 18:00</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>2680036.IB</t>
+          <t>012682444.IB</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>1.48 ~ 2.48</t>
+          <t>1.20 ~ 1.90</t>
         </is>
       </c>
       <c r="H101" s="4" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>16.0</v>
+        <v>36.2</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>G26铁道6</t>
+          <t>26百业源CP003</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>29.92Y</t>
+          <t>267D</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>2.2147</t>
+          <t>1.5169</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>2.2100/2.2050</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>中国国家铁路集团有限公司</t>
+          <t>伊犁川宁生物技术股份有限公司</t>
         </is>
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>C- 18.00</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
@@ -23583,154 +23591,146 @@
       </c>
       <c r="T101" s="3" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="U101" s="4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V101" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="W101" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X101" s="3" t="inlineStr">
+        <is>
+          <t>1.77%~1.81%</t>
+        </is>
+      </c>
+      <c r="Y101" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z101" s="3"/>
+      <c r="AA101" s="3" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区</t>
+        </is>
+      </c>
+      <c r="AB101" s="3" t="inlineStr">
+        <is>
+          <t>本期发行金额2亿元，全部用于发行人本部补充营运资金</t>
+        </is>
+      </c>
+      <c r="AC101" s="3" t="inlineStr">
+        <is>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD101" s="3"/>
+      <c r="AE101" s="3" t="inlineStr">
+        <is>
+          <t>超短期融资券(SCP)</t>
+        </is>
+      </c>
+      <c r="AF101" s="3" t="inlineStr">
+        <is>
+          <t>民营企业</t>
+        </is>
+      </c>
+      <c r="AG101" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH101" s="3" t="inlineStr">
+        <is>
+          <t>伊犁川宁生物技术股份有限公司2026年度第二期超短期融资券</t>
+        </is>
+      </c>
+      <c r="AI101" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ101" s="3" t="inlineStr">
+        <is>
+          <t>2027-07-13</t>
+        </is>
+      </c>
+      <c r="AK101" s="3"/>
+      <c r="AL101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AM101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AN101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AO101" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP101" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ101" s="3" t="inlineStr">
+        <is>
+          <t>医药制造</t>
+        </is>
+      </c>
+      <c r="AR101" s="3" t="inlineStr">
+        <is>
+          <t>药品制造</t>
+        </is>
+      </c>
+      <c r="AS101" s="3" t="inlineStr">
+        <is>
+          <t>药品制造</t>
+        </is>
+      </c>
+      <c r="AT101" s="3" t="inlineStr">
+        <is>
+          <t>生物制品</t>
+        </is>
+      </c>
+      <c r="AU101" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV101" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW101" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX101" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY101" s="3" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="U101" s="4" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="V101" s="4" t="n">
-        <v>10.6739</v>
-      </c>
-      <c r="W101" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X101" s="3"/>
-      <c r="Y101" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z101" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA101" s="3" t="inlineStr">
-        <is>
-          <t>中华人民共和国</t>
-        </is>
-      </c>
-      <c r="AB101" s="3" t="inlineStr">
-        <is>
-          <t>本期债券发行募集资金100亿元，其中98.4187亿元用于铁路项目建设，1.5813亿元用于债务结构调整。上述资金的使用，将有利于增强发行人可持续发展能力。</t>
-        </is>
-      </c>
-      <c r="AC101" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,国开证券股份有限公司,华泰联合证券有限责任公司,国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD101" s="3" t="inlineStr">
-        <is>
-          <t>铁路建设基金</t>
-        </is>
-      </c>
-      <c r="AE101" s="3" t="inlineStr">
-        <is>
-          <t>政府支持债券</t>
-        </is>
-      </c>
-      <c r="AF101" s="3" t="inlineStr">
-        <is>
-          <t>中央国有企业</t>
-        </is>
-      </c>
-      <c r="AG101" s="3" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="AH101" s="3" t="inlineStr">
-        <is>
-          <t>2026年第十三期中国铁路建设债券(30年期)</t>
-        </is>
-      </c>
-      <c r="AI101" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AJ101" s="3" t="inlineStr">
-        <is>
-          <t>2056-10-15</t>
-        </is>
-      </c>
-      <c r="AK101" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AL101" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AM101" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AN101" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AO101" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP101" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ101" s="3" t="inlineStr">
-        <is>
-          <t>交通运输</t>
-        </is>
-      </c>
-      <c r="AR101" s="3" t="inlineStr">
-        <is>
-          <t>非盈利性交运服务</t>
-        </is>
-      </c>
-      <c r="AS101" s="3" t="inlineStr">
-        <is>
-          <t>非盈利性交运服务</t>
-        </is>
-      </c>
-      <c r="AT101" s="3" t="inlineStr">
-        <is>
-          <t>铁路运输</t>
-        </is>
-      </c>
-      <c r="AU101" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV101" s="3" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AW101" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX101" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY101" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AZ101" s="3"/>
